--- a/docs/planning/QA엑셀-v1/남다슬/QA 담양 중대재해 관리대상 남다슬.xlsx
+++ b/docs/planning/QA엑셀-v1/남다슬/QA 담양 중대재해 관리대상 남다슬.xlsx
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,9 +52,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="000563C1"/>
       <sz val="10.5"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -107,6 +107,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A6A6A6"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -283,7 +289,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -840,12 +846,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>이 파일</t>
+          <t>내 계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>관리대상의 시설물 대장과 시설물 위험도를 봅니다. 보완입력은 아직 역할 구분이 없어 누구나 저장되는 것이 정상입니다.</t>
+          <t>QA박안전2 (재난안전과 담당자) · QA하정수2 (내 부서 건설과 담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -855,15 +861,15 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>줄 수</t>
+          <t>이 파일</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10줄</t>
+          <t>관리대상의 시설물 대장과 시설물 위험도를 봅니다. 시설물은 모든 부서가 함께 보고, 보완입력은 아직 역할 구분이 없어 누구나 저장되는 것이 정상입니다.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -876,12 +882,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>줄 수</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>시설물 대장 → 시설물 위험도</t>
+          <t>10줄</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -894,12 +900,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>테스트 주소</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>(배포 주소를 받으면 채웁니다)</t>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>시설물 대장 → 시설물 위험도</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -912,10 +918,14 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+          <t>테스트 주소</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>https://safety.damyang.go.kr/login</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -926,7 +936,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>브라우저</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -940,10 +950,10 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시작한 날</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -951,82 +961,78 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>시작한 날</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>이렇게 하면 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>① 브라우저로 위 «테스트 주소»를 엽니다. 시트마다 맨 위에 «새 탭에서 시작» 또는 «같은 탭에서 이어서»가 적혀 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>② 화면 오른쪽 위 이름을 눌러 «누구로» 칸의 사람으로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+          <t>① 위 «테스트 주소»에서 받은 아이디·비밀번호로 로그인합니다. 로그인하면 통합 현황 화면으로 갑니다. 5번 틀리면 계정이 잠깁니다 — 담당 개발자에게 풀어 달라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>③ «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
+          <t>② 내 계정 두 개를 창 두 개에 따로 로그인해 둡니다 — 일반 창에는 QA박안전2(재난안전과), 시크릿 창(Ctrl + Shift + N · 맥 Cmd + Shift + N)에는 QA하정수2(담당 공무원). 두 창을 나란히 두면 계정을 바꿀 필요가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+          <t>③ «누구로» 칸에 적힌 계정의 창에서 «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>⑤ 실패·오류·문의면 «메모»에 한 줄 적고, 필요하면 «사진» 칸에 화면 캡처를 붙여넣습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>결과 고르는 법</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>이럴 때 고르세요</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1037,14 +1043,14 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>실패</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>성공</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
+          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1055,14 +1061,14 @@
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>오류</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>실패</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
+          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1073,14 +1079,14 @@
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>보류</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>오류</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
+          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -1091,14 +1097,14 @@
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>보류</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
+          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -1109,14 +1115,14 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>문의</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -1126,256 +1132,216 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>사진 붙이는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
+          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>누구로 — 계정 바꾸는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• 화면 오른쪽 위 이름을 누르면 사람 목록이 나옵니다. «누구로» 칸의 이름을 누르면 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>누구로 — 내 계정 두 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>• 계정은 두 개뿐입니다. «누구로» 칸에 계정 이름과 권한이 함께 적혀 있습니다. 비밀번호는 따로 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>누구</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>볼 수 있는 것</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>주로 하는 것</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과 담당자</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>대부분 이 계정 — 등록·확인·공문</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="5" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전2</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 담당자</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서 일만 한다</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+          <t>재난안전과 담당자</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>모든 부서 · «내 할일»은 전체</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>전 부서 등록·수정 · 확인 · 상신 · 독촉 — 대부분 이 계정</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="5" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="51" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>정환경</t>
+          <t>QA하정수2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>환경과 담당자</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>남의 부서 것을 못 건드리는지 볼 때</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+          <t>담당 공무원 (내 부서: 건설과)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>업무 화면은 전 부서, «내 할일»은 나에게 지정된 것만, 위험성평가 부서별 조치표·교육 이수현황은 내 부서만</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 일 · 남의 부서 것을 못 건드리는지 확인</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="5" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>오순환</t>
+          <t>QA시스템관리</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소장</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서를 보고 재촉한다</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+          <t>시스템 관리자 (김유석만)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 메뉴</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 파일 · 공문 반려(결재 대행)</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="5" t="n"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>김중대</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>중대재해팀장</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>공문 결재선(검토)을 볼 때</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과장</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다 — 등록 버튼이 없는 게 정상</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>김담양</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>군수</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>같은 서버를 6명이 함께 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>• 내가 만드는 것(교육 · 근로자 · 문서 · 위원 등)은 이름 앞에 내 이름을 붙입니다 — 예: «남다슬_집합교육». 그래야 내 것을 찾기 쉽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>• 다른 사람이 만든 것은 고치거나 지우지 않습니다. QA박안전2 계정에는 남의 것도 보이는데, 정상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>• 건수·이수율 같은 숫자는 다른 사람이 작업하는 동안 바뀔 수 있습니다. 숫자가 안 맞으면 새로고침해서 한 번 더 보고, 그래도 다르면 «실패».</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>• 오늘 날짜가 2026-07-16 으로 고정돼 있습니다. 기한·D-day는 이 날 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>• 입력한 데이터는 그 브라우저 탭에만 남습니다. 새 탭을 열면 처음 상태로 돌아갑니다(새로고침은 괜찮습니다).</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>• 파일 첨부는 파일 이름만 남습니다. 실제 파일을 열거나 받을 수는 없습니다.</t>
+          <t>• 기한·D-day는 서버의 오늘 날짜 기준입니다.</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1355,110 @@
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>• 과장·군수에게 등록·수정 버튼이 없는 것, 결재 승인·반려 버튼이 없는 것(결재는 온나라에서 합니다)은 정상입니다.</t>
+          <t>• «이러면 성공»의 «» 안 문구와 화면 글자가 조금 다르고(띄어쓰기·마침표·어순) 뜻이 같으면 «문의»로 고르고 화면 문구를 메모에 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>• 2025년 자료는 실제 문서이고, 2026년 자료는 «예시 자료»입니다.</t>
+          <t>• 온나라 연계 전까지 결재는 시스템 안에서 끝납니다 — 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시됩니다. 결재자가 로그인해 승인할 일은 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>• ---</t>
+          <t>• 로그인은 30분이 지나면 끊깁니다(작업 중이어도). 다시 로그인하고 이어서 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>• 독촉·재촉 알림은 실제 직원에게 가고 되돌릴 수 없습니다. 내 부서 건만 1건씩 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>• 과장·팀장이 담당자를 지정하는 흐름과 «내 할일»의 ‹자기 부서 전체› 보기는 과장 계정이 없어 이번 QA 범위 밖입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>• 순서를 놓쳤거나 확인할 자료가 서버에 없으면 «확인 불가»를 고르고 메모에 이유를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
+  <mergeCells count="51">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F38:H38"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="E40:H40"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"크롬,엣지,웨일,사파리,파이어폭스,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"윈도우 PC,맥,태블릿,휴대폰"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1733,7 +1724,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1753,7 +1744,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작하세요.</t>
+          <t>🗂 QA박안전2 창에서 합니다. 시설물은 새로 만들 수 없어 이미 있는 시설물을 고쳐 봅니다. 다른 사람과 겹치지 않게 계정 이름 끝 숫자로 시설물을 고르고, 번호·이름·원래 값은 메모에 적고, 4번 끝에서 원래대로 되돌립니다.</t>
         </is>
       </c>
     </row>
@@ -1804,13 +1795,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1830,20 +1821,20 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>요약 카드와 목록이 뜨고 «표시 N / 전체 M건»이 맞다</t>
+          <t>요약 카드 4개(총 시설물 · 종별 · 30년 초과 노후 · 안전등급 확보)와 목록이 뜬다. 목록 아래 «표시 N / 전체 M건»의 M이 «총 시설물» 숫자와 같다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -1858,25 +1849,27 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>검색 · 구분 · 종별 · 관할 조건 → 없는 이름(zzz) 검색 → 지운다</t>
+          <t>① 구분 · 종별 · 소관 · 평가 조건과 «노후만»을 하나씩 걸어 본다
+② 검색칸에 없는 이름(zzz)을 친다
+③ 조건과 검색어를 모두 푼다</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>조건대로 걸러지고, 없으면 «조건에 맞는 시설물이 없습니다», 지우면 전체로</t>
+          <t>조건대로 줄이 걸러지고 «표시 N»도 따라 바뀐다. 없는 이름이면 «조건에 맞는 시설물이 없습니다.», 모두 풀면 다시 전체가 보인다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -1891,25 +1884,25 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>아무 줄이나 누른다</t>
+          <t>아무 줄이나 눌러 상세를 연다 → [닫기]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>«시설물 상세 — 이름» 창에 기본현황 · 보완입력 · 위험도 · 개선조치가 보인다</t>
+          <t>«시설물 상세 — (시설물 이름)» 창에 FMS 기본현황 · 보완입력 · 시설물 위험도 · 개선조치 내역이 보인다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="261" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -1919,30 +1912,34 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>보완입력 저장</t>
+          <t>보완입력 저장과 되돌리기</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>등급 없는 시설물 → 점검일 2027-01-01 저장 → 규모 -5 저장 → 등급 D · 점검일 2026-03-02 · 규모 120 m 저장</t>
+          <t>① 평가 조건을 «등급 없음»으로 두고, 목록 위에서부터 세어 계정 이름 끝 숫자번째 줄을 연다(끝 숫자가 3이면 3번째 줄). 시설물 번호 · 이름과 원래 최근 점검일 · 규모 · 단위, 목록의 위험도를 메모에 적는다
+② 최근 점검일을 내일 날짜로 넣고 [보완입력 저장]
+③ 점검일을 비우고 규모 -5, 단위 m로 [보완입력 저장]
+④ 안전등급 D · 최근 점검일 어제 · 규모 120, 단위 m로 [보완입력 저장] → 메모한 시설물 번호를 검색칸에 붙여넣어 찾는다(검색칸은 한 글자씩 치면 끊길 수 있다 — 붙여넣는다)
+⑤ 다시 상세를 열어 안전등급을 «미평가»로, 최근 점검일 · 규모 · 단위를 ①에서 메모한 원래 값(없었으면 빈칸)으로 돌려 [보완입력 저장]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>미래 날짜·음수는 막히고, 바른 값은 «보완입력 저장됨» 후 목록의 등급·위험도가 바뀐다</t>
+          <t>②는 «점검일은 미래일 수 없습니다.», ③은 «규모 값과 단위를 올바르게 입력하세요 — 0 이상 숫자입니다.»로 막힌다. ④는 «보완입력 저장됨» 뒤 그 줄이 «D등급»과 점수 있는 위험도로 바뀐다. ⑤ 뒤에는 ①에서 본 등급 · 위험도로 돌아간다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="111" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -1952,30 +1949,31 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>변경 이력</t>
+          <t>연계 · 변경 이력</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>[연계·변경 이력 (N)]을 누른다</t>
+          <t>① 4번을 끝내자마자 목록 위 [연계·변경 이력 (N)]을 누른다
+② 4번에서 고친 시설물 번호로 줄을 찾는다</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>목록 아래 이력 표 맨 위에 방금 저장한 것이 있다. [FMS 연계] 버튼은 없다</t>
+          <t>목록 아래 «연계 · 변경 이력 (감사추적)» 표로 내려가고, 시설물 칸이 그 시설물 번호인 «보완입력» · «저장» 줄이 있다(4번에서 바꾼 것과 되돌린 것). 다른 사람 줄이 많아 20건 밖으로 밀렸으면(표 아래 «최근 20건 표시 / 전체 N건») «확인 불가». 목록 위에 [FMS 연계] 버튼은 없다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="28" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -1990,12 +1988,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>상세의 [FMS 전송(수정)] → [취소] → 다시 → [전송]</t>
+          <t>① 4번에서 고친 시설물의 상세 → [FMS 전송(수정)]
+② 확인 창 내용을 읽고 [취소]한다(FMS 실연계라 [전송]은 누르지 않는다)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>바로 보내지 않고 확인 화면이 뜬다. 전송하면 이력에 남는다</t>
+          <t>바로 보내지 않고 «FMS 전송 확인 — (시설물 이름)» 창이 뜬다. 창에 시설물번호(반영키)와 updateBastbMaster가 보이고, [취소]하면 상세로 돌아온다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
@@ -2054,7 +2053,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2074,7 +2073,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
+          <t>🗂 QA박안전2 창에서 하고, 마지막 줄만 QA하정수2 창에서 합니다. 8번에서 고친 시설물은 같은 줄에서 원래대로 되돌립니다. 위험성평가로 넘어가도 행은 추가하지 않습니다 — 정기평가는 6명이 함께 쓰는 1건입니다.</t>
         </is>
       </c>
     </row>
@@ -2125,13 +2124,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>7</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2141,30 +2140,30 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>순서와 산정 불가</t>
+          <t>순서와 산정불가</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>메뉴로 들어간다</t>
+          <t>메뉴로 들어가 목록을 위에서 아래로 훑어본다</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>높음 → 보통 → 낮음 → 산정 불가 순이다. 산정 불가 줄은 점수 없이 [보완입력]만 있다</t>
+          <t>위험도가 높음 → 보통 → 낮음 → 산정불가 순이다. 산정불가 줄은 점수가 없고 버튼이 [보완입력]이다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="111" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>8</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -2179,25 +2178,27 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>산정 불가 줄 [보완입력] → 등급 C 저장</t>
+          <t>① 산정불가 줄 가운데 맨 아래에서부터 세어 계정 이름 끝 숫자번째 줄의 [보완입력]을 누른다(번호 · 이름은 메모에)
+② 안전등급 C만 골라 [보완입력 저장]
+③ 관리대상 &gt; 시설물 대장 메뉴에서 메모한 시설물 번호를 검색칸에 붙여넣어 상세를 열고, 안전등급을 «미평가»로 돌려 [보완입력 저장]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>새로고침 없이 순위 안으로 올라가고 산정 불가가 1 준다</t>
+          <t>② 뒤 새로고침 없이 그 시설물이 점수와 함께 순위 안으로 올라가고 위 «산정 불가» 카드 숫자가 줄어든다. ③ 뒤에는 다시 «산정불가»다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>9</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -2212,25 +2213,26 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>점수 있는 줄의 [근로자 위험성평가 연계]</t>
+          <t>① 점수가 있는 줄의 [근로자 위험성평가 연계](개선조치가 있는 줄은 [연계 보기])를 누른다
+② 넘어간 화면 위 안내를 읽는다 — 행은 추가하지 않는다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>정기 위험성평가로 가고 «시설물 ○○ 에서 넘어왔습니다» 안내가 있다</t>
+          <t>정기 위험성평가 화면으로 가고 위에 «시설물 (그 이름) 에서 넘어왔습니다 — …» 안내가 있다(뒤 문장은 평가 진행 단계마다 다르다)</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="81" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>10</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>김담양</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -2240,17 +2242,19 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>군수 화면</t>
+          <t>담당 공무원도 시설물은 모두 본다</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>조건 드롭다운을 바꿔 본다</t>
+          <t>① QA하정수2 창에서 시설물 위험도를 열어 필터 줄 오른쪽 «N / M건»을 본다
+② 구분 · 종별 · 소관 조건을 바꿔 본다
+③ 관리대상 &gt; 시설물 대장에서 목록 아래 «전체 M건»을 본다</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>조건대로 바뀌고 오류가 없다</t>
+          <t>두 화면의 M이 QA박안전2 창의 같은 화면과 같다(시설물은 아직 부서 구분이 없다 — 정상). 조건대로 바뀌고 오류가 없다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
@@ -2375,7 +2379,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
